--- a/outputs/reports/stacked_ensemble_v1/evaluation.xlsx
+++ b/outputs/reports/stacked_ensemble_v1/evaluation.xlsx
@@ -487,37 +487,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9549620577510595</v>
+        <v>0.9551869473426552</v>
       </c>
       <c r="C2" t="n">
-        <v>0.07019076743847386</v>
+        <v>0.06791942033601402</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9737373737373738</v>
+        <v>0.9872685185185185</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1309426786199402</v>
+        <v>0.1270952842136631</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9548964065469084</v>
+        <v>0.9550805832693784</v>
       </c>
       <c r="G2" t="n">
-        <v>135178</v>
+        <v>248894</v>
       </c>
       <c r="H2" t="n">
-        <v>6385</v>
+        <v>11706</v>
       </c>
       <c r="I2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J2" t="n">
-        <v>482</v>
+        <v>853</v>
       </c>
       <c r="K2" t="n">
-        <v>0.9904099948504206</v>
+        <v>0.995863958439925</v>
       </c>
       <c r="L2" t="n">
-        <v>0.964880059813097</v>
+        <v>0.9686802573397485</v>
       </c>
     </row>
   </sheetData>
@@ -613,43 +613,43 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003484492249644511</v>
+        <v>0.003304470213872656</v>
       </c>
       <c r="C2" t="n">
-        <v>1421</v>
+        <v>2615</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3391977480647431</v>
+        <v>0.324282982791587</v>
       </c>
       <c r="E2" t="n">
-        <v>97.34495695875006</v>
+        <v>98.1346363571985</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9737373737373738</v>
+        <v>0.9814814814814815</v>
       </c>
       <c r="G2" t="n">
-        <v>7103</v>
+        <v>13074</v>
       </c>
       <c r="H2" t="n">
-        <v>0.06785865127410953</v>
+        <v>0.06524399571668961</v>
       </c>
       <c r="I2" t="n">
-        <v>19.47447329837869</v>
+        <v>19.74416214822747</v>
       </c>
       <c r="J2" t="n">
-        <v>0.9737373737373738</v>
+        <v>0.9872685185185185</v>
       </c>
       <c r="K2" t="n">
-        <v>14206</v>
+        <v>26147</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03392932563705477</v>
+        <v>0.03273798141278158</v>
       </c>
       <c r="M2" t="n">
-        <v>9.737236649189345</v>
+        <v>9.907180060314262</v>
       </c>
       <c r="N2" t="n">
-        <v>0.9737373737373738</v>
+        <v>0.9907407407407407</v>
       </c>
     </row>
   </sheetData>
@@ -700,13 +700,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>80782</v>
+        <v>152483</v>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>4.951598128295907e-05</v>
+        <v>1.311621623394083e-05</v>
       </c>
       <c r="E2" t="b">
         <v>0</v>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>33200</v>
+        <v>59487</v>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0001807228915662651</v>
+        <v>6.724158219442903e-05</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
@@ -738,13 +738,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11854</v>
+        <v>20635</v>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0002530791294077948</v>
+        <v>9.69227041434456e-05</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5814</v>
+        <v>10116</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -776,13 +776,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3530</v>
+        <v>6166</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>0.0004865390853065196</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
@@ -795,13 +795,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2255</v>
+        <v>4004</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>0.0004995004995004995</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
@@ -814,13 +814,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1519</v>
+        <v>2734</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>0.000365764447695684</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1092</v>
+        <v>1985</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -852,13 +852,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>822</v>
+        <v>1582</v>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>0.00121654501216545</v>
+        <v>0.001896333754740834</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
@@ -871,13 +871,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1190</v>
+        <v>2272</v>
       </c>
       <c r="C11" t="n">
-        <v>481</v>
+        <v>847</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4042016806722689</v>
+        <v>0.3727992957746479</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>

--- a/outputs/reports/stacked_ensemble_v1/evaluation.xlsx
+++ b/outputs/reports/stacked_ensemble_v1/evaluation.xlsx
@@ -487,37 +487,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9551869473426552</v>
+        <v>0.9547509408561026</v>
       </c>
       <c r="C2" t="n">
-        <v>0.06791942033601402</v>
+        <v>0.06386020651310564</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9872685185185185</v>
+        <v>0.9469964664310954</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1270952842136631</v>
+        <v>0.1196517598035568</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9550805832693784</v>
+        <v>0.9547762024442185</v>
       </c>
       <c r="G2" t="n">
-        <v>248894</v>
+        <v>248829</v>
       </c>
       <c r="H2" t="n">
-        <v>11706</v>
+        <v>11786</v>
       </c>
       <c r="I2" t="n">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="J2" t="n">
-        <v>853</v>
+        <v>804</v>
       </c>
       <c r="K2" t="n">
-        <v>0.995863958439925</v>
+        <v>0.9822966410407276</v>
       </c>
       <c r="L2" t="n">
-        <v>0.9686802573397485</v>
+        <v>0.8596319260463616</v>
       </c>
     </row>
   </sheetData>
@@ -613,43 +613,43 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003304470213872656</v>
+        <v>0.003247100939326255</v>
       </c>
       <c r="C2" t="n">
         <v>2615</v>
       </c>
       <c r="D2" t="n">
-        <v>0.324282982791587</v>
+        <v>0.2978967495219885</v>
       </c>
       <c r="E2" t="n">
-        <v>98.1346363571985</v>
+        <v>91.74237422499081</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9814814814814815</v>
+        <v>0.917550058892815</v>
       </c>
       <c r="G2" t="n">
         <v>13074</v>
       </c>
       <c r="H2" t="n">
-        <v>0.06524399571668961</v>
+        <v>0.06164907449900566</v>
       </c>
       <c r="I2" t="n">
-        <v>19.74416214822747</v>
+        <v>18.98588176066904</v>
       </c>
       <c r="J2" t="n">
-        <v>0.9872685185185185</v>
+        <v>0.9493521790341578</v>
       </c>
       <c r="K2" t="n">
         <v>26147</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03273798141278158</v>
+        <v>0.03101694267028722</v>
       </c>
       <c r="M2" t="n">
-        <v>9.907180060314262</v>
+        <v>9.552195404409868</v>
       </c>
       <c r="N2" t="n">
-        <v>0.9907407407407407</v>
+        <v>0.9552414605418139</v>
       </c>
     </row>
   </sheetData>
@@ -700,13 +700,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>152483</v>
+        <v>144571</v>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D2" t="n">
-        <v>1.311621623394083e-05</v>
+        <v>7.60871820766267e-05</v>
       </c>
       <c r="E2" t="b">
         <v>0</v>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>59487</v>
+        <v>64688</v>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D3" t="n">
-        <v>6.724158219442903e-05</v>
+        <v>0.0002937175364828098</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
@@ -738,13 +738,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20635</v>
+        <v>22366</v>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>9.69227041434456e-05</v>
+        <v>0.0003129750514173299</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10116</v>
+        <v>10874</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>0.0004598123965422108</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -776,13 +776,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6166</v>
+        <v>6356</v>
       </c>
       <c r="C6" t="n">
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0004865390853065196</v>
+        <v>0.0004719949653870359</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
@@ -795,13 +795,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4004</v>
+        <v>4267</v>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0004995004995004995</v>
+        <v>0.0007030700726505742</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
@@ -814,13 +814,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2734</v>
+        <v>2900</v>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D8" t="n">
-        <v>0.000365764447695684</v>
+        <v>0.002758620689655172</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
@@ -833,13 +833,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1985</v>
+        <v>2101</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>0.003807710613993336</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
@@ -852,13 +852,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1582</v>
+        <v>1365</v>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D10" t="n">
-        <v>0.001896333754740834</v>
+        <v>0.008058608058608059</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
@@ -871,13 +871,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2272</v>
+        <v>1976</v>
       </c>
       <c r="C11" t="n">
-        <v>847</v>
+        <v>774</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3727992957746479</v>
+        <v>0.3917004048582996</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>

--- a/outputs/reports/stacked_ensemble_v1/evaluation.xlsx
+++ b/outputs/reports/stacked_ensemble_v1/evaluation.xlsx
@@ -487,37 +487,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9547509408561026</v>
+        <v>0.9658454356846473</v>
       </c>
       <c r="C2" t="n">
-        <v>0.06386020651310564</v>
+        <v>0.05405405405405406</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9469964664310954</v>
+        <v>0.4320987654320987</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1196517598035568</v>
+        <v>0.09608785175017158</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9547762024442185</v>
+        <v>0.9680972967342049</v>
       </c>
       <c r="G2" t="n">
-        <v>248829</v>
+        <v>37173</v>
       </c>
       <c r="H2" t="n">
-        <v>11786</v>
+        <v>1225</v>
       </c>
       <c r="I2" t="n">
-        <v>45</v>
+        <v>92</v>
       </c>
       <c r="J2" t="n">
-        <v>804</v>
+        <v>70</v>
       </c>
       <c r="K2" t="n">
-        <v>0.9822966410407276</v>
+        <v>0.868122391276809</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8596319260463616</v>
+        <v>0.1929882545969052</v>
       </c>
     </row>
   </sheetData>
@@ -613,43 +613,43 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003247100939326255</v>
+        <v>0.004201244813278008</v>
       </c>
       <c r="C2" t="n">
-        <v>2615</v>
+        <v>386</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2978967495219885</v>
+        <v>0.1373056994818653</v>
       </c>
       <c r="E2" t="n">
-        <v>91.74237422499081</v>
+        <v>32.68214674086867</v>
       </c>
       <c r="F2" t="n">
-        <v>0.917550058892815</v>
+        <v>0.3271604938271605</v>
       </c>
       <c r="G2" t="n">
-        <v>13074</v>
+        <v>1928</v>
       </c>
       <c r="H2" t="n">
-        <v>0.06164907449900566</v>
+        <v>0.04512448132780083</v>
       </c>
       <c r="I2" t="n">
-        <v>18.98588176066904</v>
+        <v>10.74074074074074</v>
       </c>
       <c r="J2" t="n">
-        <v>0.9493521790341578</v>
+        <v>0.5370370370370371</v>
       </c>
       <c r="K2" t="n">
-        <v>26147</v>
+        <v>3856</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03101694267028722</v>
+        <v>0.02645228215767635</v>
       </c>
       <c r="M2" t="n">
-        <v>9.552195404409868</v>
+        <v>6.296296296296297</v>
       </c>
       <c r="N2" t="n">
-        <v>0.9552414605418139</v>
+        <v>0.6296296296296297</v>
       </c>
     </row>
   </sheetData>
@@ -700,13 +700,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>144571</v>
+        <v>29710</v>
       </c>
       <c r="C2" t="n">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="D2" t="n">
-        <v>7.60871820766267e-05</v>
+        <v>0.001312689330191855</v>
       </c>
       <c r="E2" t="b">
         <v>0</v>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>64688</v>
+        <v>4848</v>
       </c>
       <c r="C3" t="n">
         <v>19</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0002937175364828098</v>
+        <v>0.003919141914191419</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
@@ -738,13 +738,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>22366</v>
+        <v>1510</v>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0003129750514173299</v>
+        <v>0.00728476821192053</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10874</v>
+        <v>716</v>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0004598123965422108</v>
+        <v>0.01396648044692737</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -776,13 +776,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6356</v>
+        <v>478</v>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0004719949653870359</v>
+        <v>0.02719665271966527</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
@@ -795,13 +795,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4267</v>
+        <v>365</v>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0007030700726505742</v>
+        <v>0.01095890410958904</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
@@ -814,13 +814,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2900</v>
+        <v>311</v>
       </c>
       <c r="C8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D8" t="n">
-        <v>0.002758620689655172</v>
+        <v>0.02893890675241157</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
@@ -833,13 +833,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2101</v>
+        <v>246</v>
       </c>
       <c r="C9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>0.003807710613993336</v>
+        <v>0.02032520325203252</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
@@ -852,13 +852,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1365</v>
+        <v>206</v>
       </c>
       <c r="C10" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>0.008058608058608059</v>
+        <v>0.01941747572815534</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
@@ -871,13 +871,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1976</v>
+        <v>170</v>
       </c>
       <c r="C11" t="n">
-        <v>774</v>
+        <v>48</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3917004048582996</v>
+        <v>0.2823529411764706</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>
